--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1857,6 +1857,117 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128383872</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90862</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Musåkringlan, Musåkringlan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>497207</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6773656</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128365158</v>
       </c>
       <c r="B2" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128365143</v>
       </c>
       <c r="B3" t="n">
-        <v>97350</v>
+        <v>97355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128365157</v>
       </c>
       <c r="B4" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128365144</v>
       </c>
       <c r="B5" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128365156</v>
+        <v>128365145</v>
       </c>
       <c r="B6" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497268</v>
+        <v>497264</v>
       </c>
       <c r="R6" t="n">
-        <v>6773860</v>
+        <v>6774013</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,6 +1193,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1211,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128365145</v>
+        <v>128365156</v>
       </c>
       <c r="B7" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497264</v>
+        <v>497268</v>
       </c>
       <c r="R7" t="n">
-        <v>6774013</v>
+        <v>6773860</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,7 +1282,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1291,7 +1292,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,7 +1301,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>128365161</v>
       </c>
       <c r="B8" t="n">
-        <v>57776</v>
+        <v>57777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128365139</v>
+        <v>128365154</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1437,21 +1437,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497220</v>
+        <v>497232</v>
       </c>
       <c r="R9" t="n">
-        <v>6774011</v>
+        <v>6774036</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,7 +1536,7 @@
         <v>128365155</v>
       </c>
       <c r="B10" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128365154</v>
+        <v>128365139</v>
       </c>
       <c r="B11" t="n">
-        <v>79031</v>
+        <v>57670</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,21 +1651,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497232</v>
+        <v>497220</v>
       </c>
       <c r="R11" t="n">
-        <v>6774036</v>
+        <v>6774011</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128365158</v>
       </c>
       <c r="B2" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128365143</v>
       </c>
       <c r="B3" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128365157</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128365144</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128365145</v>
+        <v>128365156</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497264</v>
+        <v>497268</v>
       </c>
       <c r="R6" t="n">
-        <v>6774013</v>
+        <v>6773860</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,7 +1193,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1212,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128365156</v>
+        <v>128365145</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497268</v>
+        <v>497264</v>
       </c>
       <c r="R7" t="n">
-        <v>6773860</v>
+        <v>6774013</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,7 +1281,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1292,7 +1291,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,6 +1300,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>128365161</v>
       </c>
       <c r="B8" t="n">
-        <v>57777</v>
+        <v>57789</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>128365154</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>128365155</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>128365139</v>
       </c>
       <c r="B11" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>128384041</v>
       </c>
       <c r="B12" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>128383872</v>
       </c>
       <c r="B13" t="n">
-        <v>90862</v>
+        <v>90954</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -1104,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128365156</v>
+        <v>128365145</v>
       </c>
       <c r="B6" t="n">
         <v>79083</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497268</v>
+        <v>497264</v>
       </c>
       <c r="R6" t="n">
-        <v>6773860</v>
+        <v>6774013</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,6 +1193,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1211,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128365145</v>
+        <v>128365156</v>
       </c>
       <c r="B7" t="n">
         <v>79083</v>
@@ -1246,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497264</v>
+        <v>497268</v>
       </c>
       <c r="R7" t="n">
-        <v>6774013</v>
+        <v>6773860</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,7 +1282,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1291,7 +1292,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,7 +1301,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -1862,7 +1862,7 @@
         <v>128383872</v>
       </c>
       <c r="B13" t="n">
-        <v>90954</v>
+        <v>90960</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128365158</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128365143</v>
       </c>
       <c r="B3" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128365157</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128365144</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>128365145</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>128365156</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>128365161</v>
       </c>
       <c r="B8" t="n">
-        <v>57789</v>
+        <v>57793</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>128365154</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128365155</v>
+        <v>128365139</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>57686</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497218</v>
+        <v>497220</v>
       </c>
       <c r="R10" t="n">
-        <v>6773986</v>
+        <v>6774011</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128365139</v>
+        <v>128365155</v>
       </c>
       <c r="B11" t="n">
-        <v>57682</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,21 +1651,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497220</v>
+        <v>497218</v>
       </c>
       <c r="R11" t="n">
-        <v>6774011</v>
+        <v>6773986</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,7 +1750,7 @@
         <v>128384041</v>
       </c>
       <c r="B12" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>128383872</v>
       </c>
       <c r="B13" t="n">
-        <v>90960</v>
+        <v>90966</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128365158</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128365143</v>
       </c>
       <c r="B3" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128365157</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128365144</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>128365145</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>128365156</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>128365154</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128365139</v>
+        <v>128365155</v>
       </c>
       <c r="B10" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,21 +1544,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497220</v>
+        <v>497218</v>
       </c>
       <c r="R10" t="n">
-        <v>6774011</v>
+        <v>6773986</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128365155</v>
+        <v>128365139</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,21 +1651,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497218</v>
+        <v>497220</v>
       </c>
       <c r="R11" t="n">
-        <v>6773986</v>
+        <v>6774011</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,7 +1862,7 @@
         <v>128383872</v>
       </c>
       <c r="B13" t="n">
-        <v>90966</v>
+        <v>90968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128365154</v>
+        <v>128365139</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1437,21 +1437,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497232</v>
+        <v>497220</v>
       </c>
       <c r="R9" t="n">
-        <v>6774036</v>
+        <v>6774011</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128365155</v>
+        <v>128365154</v>
       </c>
       <c r="B10" t="n">
         <v>79089</v>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497218</v>
+        <v>497232</v>
       </c>
       <c r="R10" t="n">
-        <v>6773986</v>
+        <v>6774036</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128365139</v>
+        <v>128365155</v>
       </c>
       <c r="B11" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,21 +1651,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497220</v>
+        <v>497218</v>
       </c>
       <c r="R11" t="n">
-        <v>6774011</v>
+        <v>6773986</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>128365143</v>
       </c>
       <c r="B3" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128365145</v>
+        <v>128365156</v>
       </c>
       <c r="B6" t="n">
         <v>79089</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497264</v>
+        <v>497268</v>
       </c>
       <c r="R6" t="n">
-        <v>6774013</v>
+        <v>6773860</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,7 +1193,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1212,7 +1211,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128365156</v>
+        <v>128365145</v>
       </c>
       <c r="B7" t="n">
         <v>79089</v>
@@ -1247,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497268</v>
+        <v>497264</v>
       </c>
       <c r="R7" t="n">
-        <v>6773860</v>
+        <v>6774013</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,7 +1281,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1292,7 +1291,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,6 +1300,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128365139</v>
+        <v>128365154</v>
       </c>
       <c r="B9" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1437,21 +1437,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497220</v>
+        <v>497232</v>
       </c>
       <c r="R9" t="n">
-        <v>6774011</v>
+        <v>6774036</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128365154</v>
+        <v>128365155</v>
       </c>
       <c r="B10" t="n">
         <v>79089</v>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497232</v>
+        <v>497218</v>
       </c>
       <c r="R10" t="n">
-        <v>6774036</v>
+        <v>6773986</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128365155</v>
+        <v>128365139</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,21 +1651,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497218</v>
+        <v>497220</v>
       </c>
       <c r="R11" t="n">
-        <v>6773986</v>
+        <v>6774011</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,7 +1862,7 @@
         <v>128383872</v>
       </c>
       <c r="B13" t="n">
-        <v>90968</v>
+        <v>90969</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -1862,7 +1862,7 @@
         <v>128383872</v>
       </c>
       <c r="B13" t="n">
-        <v>90969</v>
+        <v>90996</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128365158</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128365143</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128365157</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128365144</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128365156</v>
+        <v>128365145</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497268</v>
+        <v>497264</v>
       </c>
       <c r="R6" t="n">
-        <v>6773860</v>
+        <v>6774013</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,6 +1193,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1211,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128365145</v>
+        <v>128365156</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497264</v>
+        <v>497268</v>
       </c>
       <c r="R7" t="n">
-        <v>6774013</v>
+        <v>6773860</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,7 +1282,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1291,7 +1292,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,7 +1301,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>128365161</v>
       </c>
       <c r="B8" t="n">
-        <v>57793</v>
+        <v>57820</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128365154</v>
+        <v>128365139</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>57713</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1437,21 +1437,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497232</v>
+        <v>497220</v>
       </c>
       <c r="R9" t="n">
-        <v>6774036</v>
+        <v>6774011</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,7 +1536,7 @@
         <v>128365155</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128365139</v>
+        <v>128365154</v>
       </c>
       <c r="B11" t="n">
-        <v>57686</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,21 +1651,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497220</v>
+        <v>497232</v>
       </c>
       <c r="R11" t="n">
-        <v>6774011</v>
+        <v>6774036</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,7 +1750,7 @@
         <v>128384041</v>
       </c>
       <c r="B12" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -1533,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128365155</v>
+        <v>128365154</v>
       </c>
       <c r="B10" t="n">
         <v>79116</v>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497218</v>
+        <v>497232</v>
       </c>
       <c r="R10" t="n">
-        <v>6773986</v>
+        <v>6774036</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,7 +1640,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128365154</v>
+        <v>128365155</v>
       </c>
       <c r="B11" t="n">
         <v>79116</v>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497232</v>
+        <v>497218</v>
       </c>
       <c r="R11" t="n">
-        <v>6774036</v>
+        <v>6773986</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,7 +1862,7 @@
         <v>128383872</v>
       </c>
       <c r="B13" t="n">
-        <v>90996</v>
+        <v>91001</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128365158</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128365143</v>
       </c>
       <c r="B3" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128365157</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128365144</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>128365145</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>128365156</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128365139</v>
+        <v>128365154</v>
       </c>
       <c r="B9" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1437,21 +1437,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497220</v>
+        <v>497232</v>
       </c>
       <c r="R9" t="n">
-        <v>6774011</v>
+        <v>6774036</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128365154</v>
+        <v>128365155</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497232</v>
+        <v>497218</v>
       </c>
       <c r="R10" t="n">
-        <v>6774036</v>
+        <v>6773986</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1640,10 +1640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128365155</v>
+        <v>128365139</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1651,21 +1651,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497218</v>
+        <v>497220</v>
       </c>
       <c r="R11" t="n">
-        <v>6773986</v>
+        <v>6774011</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,7 +1862,7 @@
         <v>128383872</v>
       </c>
       <c r="B13" t="n">
-        <v>91001</v>
+        <v>91006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -1104,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128365145</v>
+        <v>128365156</v>
       </c>
       <c r="B6" t="n">
         <v>79120</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497264</v>
+        <v>497268</v>
       </c>
       <c r="R6" t="n">
-        <v>6774013</v>
+        <v>6773860</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,7 +1193,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1212,7 +1211,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128365156</v>
+        <v>128365145</v>
       </c>
       <c r="B7" t="n">
         <v>79120</v>
@@ -1247,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497268</v>
+        <v>497264</v>
       </c>
       <c r="R7" t="n">
-        <v>6773860</v>
+        <v>6774013</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,7 +1281,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1292,7 +1291,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,6 +1300,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>128383872</v>
       </c>
       <c r="B13" t="n">
-        <v>91006</v>
+        <v>91010</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128365158</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128365143</v>
       </c>
       <c r="B3" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128365157</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128365144</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>128365156</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>128365145</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>128365161</v>
       </c>
       <c r="B8" t="n">
-        <v>57820</v>
+        <v>57824</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>128365154</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>128365155</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
         <v>128365139</v>
       </c>
       <c r="B11" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>128384041</v>
       </c>
       <c r="B12" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -1750,7 +1750,7 @@
         <v>128384041</v>
       </c>
       <c r="B12" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>128383872</v>
       </c>
       <c r="B13" t="n">
-        <v>91010</v>
+        <v>91015</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128365158</v>
+        <v>128365144</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497267</v>
+        <v>497262</v>
       </c>
       <c r="R2" t="n">
-        <v>6773855</v>
+        <v>6774020</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,6 +764,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,32 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128365143</v>
+        <v>128365145</v>
       </c>
       <c r="B3" t="n">
-        <v>97507</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497269</v>
+        <v>497264</v>
       </c>
       <c r="R3" t="n">
-        <v>6773880</v>
+        <v>6774013</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,14 +891,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128365157</v>
+        <v>128365154</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -924,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497265</v>
+        <v>497232</v>
       </c>
       <c r="R4" t="n">
-        <v>6773860</v>
+        <v>6774036</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +961,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +971,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,14 +998,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128365144</v>
+        <v>128365155</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1031,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497262</v>
+        <v>497218</v>
       </c>
       <c r="R5" t="n">
-        <v>6774020</v>
+        <v>6773986</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1068,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1078,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,7 +1087,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1107,11 +1108,11 @@
         <v>128365156</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1211,14 +1212,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128365145</v>
+        <v>128365157</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1246,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497264</v>
+        <v>497265</v>
       </c>
       <c r="R7" t="n">
-        <v>6774013</v>
+        <v>6773860</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,7 +1282,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1291,7 +1292,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,7 +1301,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1319,32 +1319,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128365161</v>
+        <v>128365158</v>
       </c>
       <c r="B8" t="n">
-        <v>57824</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>497258</v>
+        <v>497267</v>
       </c>
       <c r="R8" t="n">
-        <v>6773852</v>
+        <v>6773855</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,32 +1426,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128365154</v>
+        <v>128365139</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497232</v>
+        <v>497220</v>
       </c>
       <c r="R9" t="n">
-        <v>6774036</v>
+        <v>6774011</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,48 +1533,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128365155</v>
+        <v>128383823</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gräftmyren, Dlr</t>
+          <t>Musåkringlan, Musåkringlan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497218</v>
+        <v>497189</v>
       </c>
       <c r="R10" t="n">
-        <v>6773986</v>
+        <v>6773647</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1613,7 +1613,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födohål</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,26 +1633,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128365139</v>
+        <v>128383933</v>
       </c>
       <c r="B11" t="n">
-        <v>57717</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1671,17 +1676,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gräftmyren, Dlr</t>
+          <t>Musåkringlan, Musåkringlan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497220</v>
+        <v>497184</v>
       </c>
       <c r="R11" t="n">
-        <v>6774011</v>
+        <v>6773624</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1710,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1720,7 +1725,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födohål</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,26 +1745,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128384041</v>
+        <v>128383999</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1782,10 +1792,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497261</v>
+        <v>497291</v>
       </c>
       <c r="R12" t="n">
-        <v>6773723</v>
+        <v>6773714</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1817,7 +1827,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1827,7 +1837,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1859,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128383872</v>
+        <v>128384041</v>
       </c>
       <c r="B13" t="n">
-        <v>91017</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,37 +1880,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>256703</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Musåkringlan, Musåkringlan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497207</v>
+        <v>497261</v>
       </c>
       <c r="R13" t="n">
-        <v>6773656</v>
+        <v>6773723</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1932,7 +1939,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1949,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födohål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,7 +1963,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1967,6 +1978,678 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128365135</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gräftmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>497290</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6773893</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack högt upp i tall.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128365136</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gräftmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>497299</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6774036</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack högt upp i tall. Osäker om äldre eller färska spår</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128365161</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gräftmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>497258</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6773852</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128365142</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gräftmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>497186</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6773746</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128365143</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gräftmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>497269</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6773880</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128383872</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Musåkringlan, Musåkringlan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>497207</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6773656</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22172-2025 artfynd.xlsx
+++ b/artfynd/A 22172-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365144</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365145</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365154</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365155</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365156</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365157</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1423,6 +1458,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365158</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1530,6 +1570,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365139</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128383823</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1754,6 +1804,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128383933</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1866,6 +1921,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128383999</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1978,6 +2038,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384041</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2098,6 +2163,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365135</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2218,6 +2288,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365136</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2325,6 +2400,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365161</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2432,6 +2512,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365142</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2539,6 +2624,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128365143</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2650,8 +2740,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128383872</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>